--- a/data/market-sweeps/Turkey.xlsx
+++ b/data/market-sweeps/Turkey.xlsx
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -128,6 +128,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E522"/>
+  <dimension ref="A1:F522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -529,6 +530,11 @@
           <t>exchange</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -556,6 +562,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -583,6 +590,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -610,6 +618,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -637,6 +646,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -664,6 +674,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -691,6 +702,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -718,6 +730,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -745,6 +758,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -772,6 +786,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -799,6 +814,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -826,6 +842,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -853,6 +870,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -880,6 +898,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -907,6 +926,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -934,6 +954,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -961,6 +982,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -988,6 +1010,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1015,6 +1038,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1042,6 +1066,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1069,6 +1094,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1096,6 +1122,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1123,6 +1150,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1150,6 +1178,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1177,6 +1206,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1204,6 +1234,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1231,6 +1262,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1258,6 +1290,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1285,6 +1318,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1312,6 +1346,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1339,6 +1374,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1366,6 +1402,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1393,6 +1430,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1420,6 +1458,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1447,6 +1486,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1474,6 +1514,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1501,6 +1542,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1528,6 +1570,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1555,6 +1598,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1582,6 +1626,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1609,6 +1654,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1636,6 +1682,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1663,6 +1710,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1690,6 +1738,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1717,6 +1766,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1744,6 +1794,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1771,6 +1822,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1798,6 +1850,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1825,6 +1878,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1852,6 +1906,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1879,6 +1934,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1906,6 +1962,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1933,6 +1990,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1960,6 +2018,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1987,6 +2046,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2014,6 +2074,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2041,6 +2102,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2068,6 +2130,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2095,6 +2158,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F59" s="9" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2122,6 +2186,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F60" s="9" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2149,6 +2214,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2176,6 +2242,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2203,6 +2270,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F63" s="9" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2230,6 +2298,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F64" s="9" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2257,6 +2326,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F65" s="9" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2284,6 +2354,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F66" s="9" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2311,6 +2382,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F67" s="9" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2338,6 +2410,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F68" s="9" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2365,6 +2438,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F69" s="9" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2392,6 +2466,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F70" s="9" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2419,6 +2494,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F71" s="9" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2446,6 +2522,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F72" s="9" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2473,6 +2550,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F73" s="9" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2500,6 +2578,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2527,6 +2606,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F75" s="9" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2554,6 +2634,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F76" s="9" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2581,6 +2662,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F77" s="9" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2608,6 +2690,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F78" s="9" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2635,6 +2718,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F79" s="9" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2662,6 +2746,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F80" s="9" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2689,6 +2774,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F81" s="9" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2716,6 +2802,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F82" s="9" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2743,6 +2830,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F83" s="9" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2770,6 +2858,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F84" s="9" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2797,6 +2886,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F85" s="9" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2824,6 +2914,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F86" s="9" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2851,6 +2942,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F87" s="9" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2878,6 +2970,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F88" s="9" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2905,6 +2998,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F89" s="9" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2932,6 +3026,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F90" s="9" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2959,6 +3054,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2986,6 +3082,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F92" s="9" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3013,6 +3110,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F93" s="9" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3040,6 +3138,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F94" s="9" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3067,6 +3166,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F95" s="9" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3094,6 +3194,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F96" s="9" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3121,6 +3222,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F97" s="9" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3148,6 +3250,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F98" s="9" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3175,6 +3278,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F99" s="9" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3202,6 +3306,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F100" s="9" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3229,6 +3334,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F101" s="9" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3256,6 +3362,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F102" s="9" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3283,6 +3390,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F103" s="9" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3310,6 +3418,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F104" s="9" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3337,6 +3446,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F105" s="9" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3364,6 +3474,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F106" s="9" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3391,6 +3502,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F107" s="9" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3418,6 +3530,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F108" s="9" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3445,6 +3558,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F109" s="9" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3472,6 +3586,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F110" s="9" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3499,6 +3614,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F111" s="9" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3526,6 +3642,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F112" s="9" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -3553,6 +3670,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F113" s="9" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3580,6 +3698,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F114" s="9" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3607,6 +3726,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F115" s="9" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3634,6 +3754,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F116" s="9" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3661,6 +3782,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F117" s="9" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3688,6 +3810,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F118" s="9" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3715,6 +3838,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F119" s="9" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3742,6 +3866,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F120" s="9" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3769,6 +3894,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F121" s="9" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3796,6 +3922,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F122" s="9" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3823,6 +3950,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F123" s="9" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3850,6 +3978,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F124" s="9" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3877,6 +4006,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F125" s="9" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3904,6 +4034,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F126" s="9" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -3931,6 +4062,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F127" s="9" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3958,6 +4090,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F128" s="9" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3985,6 +4118,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F129" s="9" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4012,6 +4146,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F130" s="9" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -4039,6 +4174,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F131" s="9" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4066,6 +4202,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F132" s="9" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -4093,6 +4230,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F133" s="9" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4120,6 +4258,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F134" s="9" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -4147,6 +4286,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F135" s="9" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4174,6 +4314,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F136" s="9" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -4201,6 +4342,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F137" s="9" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4228,6 +4370,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F138" s="9" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -4255,6 +4398,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F139" s="9" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4282,6 +4426,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F140" s="9" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -4309,6 +4454,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F141" s="9" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4336,6 +4482,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F142" s="9" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -4363,6 +4510,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F143" s="9" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4390,6 +4538,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F144" s="9" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4417,6 +4566,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F145" s="9" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4444,6 +4594,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F146" s="9" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -4471,6 +4622,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F147" s="9" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4498,6 +4650,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F148" s="9" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -4525,6 +4678,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F149" s="9" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4552,6 +4706,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F150" s="9" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -4579,6 +4734,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F151" s="9" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4606,6 +4762,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F152" s="9" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4633,6 +4790,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F153" s="9" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4660,6 +4818,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F154" s="9" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -4687,6 +4846,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F155" s="9" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4714,6 +4874,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F156" s="9" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -4741,6 +4902,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F157" s="9" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4768,6 +4930,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F158" s="9" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4795,6 +4958,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F159" s="9" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4822,6 +4986,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F160" s="9" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -4849,6 +5014,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F161" s="9" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4876,6 +5042,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F162" s="9" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4903,6 +5070,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F163" s="9" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4930,6 +5098,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F164" s="9" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4957,6 +5126,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F165" s="9" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4984,6 +5154,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F166" s="9" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -5011,6 +5182,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F167" s="9" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5038,6 +5210,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F168" s="9" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -5065,6 +5238,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F169" s="9" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5092,6 +5266,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F170" s="9" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -5119,6 +5294,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F171" s="9" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5146,6 +5322,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F172" s="9" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -5173,6 +5350,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F173" s="9" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5200,6 +5378,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F174" s="9" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -5227,6 +5406,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F175" s="9" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5254,6 +5434,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F176" s="9" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -5281,6 +5462,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F177" s="9" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5308,6 +5490,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F178" s="9" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -5335,6 +5518,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F179" s="9" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5362,6 +5546,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F180" s="9" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -5389,6 +5574,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F181" s="9" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5416,6 +5602,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F182" s="9" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -5443,6 +5630,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F183" s="9" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5470,6 +5658,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F184" s="9" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -5497,6 +5686,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F185" s="9" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5524,6 +5714,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F186" s="9" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -5551,6 +5742,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F187" s="9" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5578,6 +5770,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F188" s="9" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -5605,6 +5798,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F189" s="9" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5632,6 +5826,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F190" s="9" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -5659,6 +5854,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F191" s="9" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5686,6 +5882,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F192" s="9" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -5713,6 +5910,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F193" s="9" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5740,6 +5938,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F194" s="9" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -5767,6 +5966,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F195" s="9" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -5794,6 +5994,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F196" s="9" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -5821,6 +6022,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F197" s="9" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5848,6 +6050,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F198" s="9" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5875,6 +6078,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F199" s="9" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -5902,6 +6106,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F200" s="9" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -5929,6 +6134,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F201" s="9" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -5956,6 +6162,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F202" s="9" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -5983,6 +6190,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F203" s="9" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6010,6 +6218,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F204" s="9" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -6037,6 +6246,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F205" s="9" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6064,6 +6274,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F206" s="9" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -6091,6 +6302,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F207" s="9" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6118,6 +6330,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F208" s="9" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -6145,6 +6358,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F209" s="9" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6172,6 +6386,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F210" s="9" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -6199,6 +6414,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F211" s="9" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6226,6 +6442,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F212" s="9" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -6253,6 +6470,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F213" s="9" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6280,6 +6498,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F214" s="9" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -6307,6 +6526,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F215" s="9" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6334,6 +6554,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F216" s="9" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -6361,6 +6582,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F217" s="9" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -6388,6 +6610,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F218" s="9" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -6415,6 +6638,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F219" s="9" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -6442,6 +6666,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F220" s="9" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -6469,6 +6694,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F221" s="9" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -6496,6 +6722,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F222" s="9" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -6523,6 +6750,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F223" s="9" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -6550,6 +6778,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F224" s="9" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -6577,6 +6806,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F225" s="9" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6604,6 +6834,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F226" s="9" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -6631,6 +6862,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F227" s="9" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6658,6 +6890,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F228" s="9" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -6685,6 +6918,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F229" s="9" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -6712,6 +6946,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F230" s="9" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -6739,6 +6974,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F231" s="9" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6766,6 +7002,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F232" s="9" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -6793,6 +7030,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F233" s="9" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -6820,6 +7058,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F234" s="9" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -6847,6 +7086,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F235" s="9" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -6874,6 +7114,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F236" s="9" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -6901,6 +7142,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F237" s="9" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -6928,6 +7170,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F238" s="9" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -6955,6 +7198,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F239" s="9" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -6982,6 +7226,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F240" s="9" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -7009,6 +7254,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F241" s="9" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -7036,6 +7282,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F242" s="9" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -7063,6 +7310,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F243" s="9" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -7090,6 +7338,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F244" s="9" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -7117,6 +7366,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F245" s="9" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -7144,6 +7394,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F246" s="9" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -7171,6 +7422,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F247" s="9" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -7198,6 +7450,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F248" s="9" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -7225,6 +7478,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F249" s="9" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -7252,6 +7506,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F250" s="9" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -7279,6 +7534,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F251" s="9" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -7306,6 +7562,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F252" s="9" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -7333,6 +7590,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F253" s="9" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7360,6 +7618,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F254" s="9" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -7387,6 +7646,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F255" s="9" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -7414,6 +7674,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F256" s="9" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -7441,6 +7702,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F257" s="9" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -7468,6 +7730,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F258" s="9" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -7495,6 +7758,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F259" s="9" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -7522,6 +7786,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F260" s="9" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -7549,6 +7814,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F261" s="9" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -7576,6 +7842,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F262" s="9" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -7603,6 +7870,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F263" s="9" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -7630,6 +7898,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F264" s="9" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -7657,6 +7926,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F265" s="9" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -7684,6 +7954,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F266" s="9" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -7711,6 +7982,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F267" s="9" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -7738,6 +8010,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F268" s="9" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -7765,6 +8038,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F269" s="9" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -7792,6 +8066,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F270" s="9" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -7819,6 +8094,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F271" s="9" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -7846,6 +8122,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F272" s="9" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -7873,6 +8150,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F273" s="9" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -7900,6 +8178,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F274" s="9" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -7927,6 +8206,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F275" s="9" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -7954,6 +8234,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F276" s="9" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -7981,6 +8262,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F277" s="9" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -8008,6 +8290,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F278" s="9" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -8035,6 +8318,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F279" s="9" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -8062,6 +8346,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F280" s="9" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -8089,6 +8374,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F281" s="9" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -8116,6 +8402,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F282" s="9" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -8143,6 +8430,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F283" s="9" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -8170,6 +8458,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F284" s="9" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -8197,6 +8486,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F285" s="9" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -8224,6 +8514,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F286" s="9" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -8251,6 +8542,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F287" s="9" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8278,6 +8570,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F288" s="9" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -8305,6 +8598,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F289" s="9" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -8332,6 +8626,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F290" s="9" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -8359,6 +8654,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F291" s="9" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -8386,6 +8682,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F292" s="9" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -8413,6 +8710,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F293" s="9" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -8440,6 +8738,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F294" s="9" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -8467,6 +8766,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F295" s="9" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -8494,6 +8794,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F296" s="9" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -8521,6 +8822,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F297" s="9" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -8548,6 +8850,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F298" s="9" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -8575,6 +8878,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F299" s="9" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -8602,6 +8906,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F300" s="9" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -8629,6 +8934,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F301" s="9" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -8656,6 +8962,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F302" s="9" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -8683,6 +8990,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F303" s="9" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -8710,6 +9018,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F304" s="9" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -8737,6 +9046,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F305" s="9" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -8764,6 +9074,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F306" s="9" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -8791,6 +9102,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F307" s="9" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -8818,6 +9130,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F308" s="9" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -8845,6 +9158,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F309" s="9" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -8872,6 +9186,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F310" s="9" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -8899,6 +9214,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F311" s="9" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -8926,6 +9242,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F312" s="9" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -8953,6 +9270,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F313" s="9" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -8980,6 +9298,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F314" s="9" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -9007,6 +9326,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F315" s="9" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -9034,6 +9354,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F316" s="9" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -9061,6 +9382,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F317" s="9" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -9088,6 +9410,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F318" s="9" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -9115,6 +9438,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F319" s="9" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -9142,6 +9466,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F320" s="9" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -9169,6 +9494,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F321" s="9" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -9196,6 +9522,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F322" s="9" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -9223,6 +9550,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F323" s="9" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -9250,6 +9578,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F324" s="9" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -9277,6 +9606,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F325" s="9" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -9304,6 +9634,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F326" s="9" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -9331,6 +9662,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F327" s="9" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -9358,6 +9690,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F328" s="9" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -9385,6 +9718,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F329" s="9" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -9412,6 +9746,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F330" s="9" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -9439,6 +9774,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F331" s="9" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -9466,6 +9802,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F332" s="9" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -9493,6 +9830,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F333" s="9" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -9520,6 +9858,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F334" s="9" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -9547,6 +9886,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F335" s="9" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9574,6 +9914,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F336" s="9" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
@@ -9601,6 +9942,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F337" s="9" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -9628,6 +9970,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F338" s="9" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -9655,6 +9998,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F339" s="9" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -9682,6 +10026,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F340" s="9" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -9709,6 +10054,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F341" s="9" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -9736,6 +10082,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F342" s="9" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -9763,6 +10110,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F343" s="9" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -9790,6 +10138,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F344" s="9" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -9817,6 +10166,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F345" s="9" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -9844,6 +10194,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F346" s="9" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -9871,6 +10222,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F347" s="9" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -9898,6 +10250,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F348" s="9" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -9925,6 +10278,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F349" s="9" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -9952,6 +10306,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F350" s="9" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -9979,6 +10334,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F351" s="9" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -10006,6 +10362,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F352" s="9" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -10033,6 +10390,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F353" s="9" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -10060,6 +10418,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F354" s="9" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -10087,6 +10446,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F355" s="9" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -10114,6 +10474,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F356" s="9" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -10141,6 +10502,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F357" s="9" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -10168,6 +10530,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F358" s="9" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -10195,6 +10558,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F359" s="9" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -10222,6 +10586,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F360" s="9" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -10249,6 +10614,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F361" s="9" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -10276,6 +10642,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F362" s="9" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -10303,6 +10670,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F363" s="9" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -10330,6 +10698,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F364" s="9" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -10357,6 +10726,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F365" s="9" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -10384,6 +10754,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F366" s="9" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -10411,6 +10782,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F367" s="9" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -10438,6 +10810,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F368" s="9" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -10465,6 +10838,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F369" s="9" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -10492,6 +10866,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F370" s="9" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -10519,6 +10894,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F371" s="9" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -10546,6 +10922,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F372" s="9" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -10573,6 +10950,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F373" s="9" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -10600,6 +10978,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F374" s="9" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -10627,6 +11006,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F375" s="9" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -10654,6 +11034,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F376" s="9" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -10681,6 +11062,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F377" s="9" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -10708,6 +11090,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F378" s="9" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
@@ -10735,6 +11118,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F379" s="9" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -10762,6 +11146,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F380" s="9" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -10789,6 +11174,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F381" s="9" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -10816,6 +11202,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F382" s="9" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -10843,6 +11230,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F383" s="9" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -10870,6 +11258,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F384" s="9" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -10897,6 +11286,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F385" s="9" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -10924,6 +11314,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F386" s="9" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -10951,6 +11342,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F387" s="9" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -10978,6 +11370,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F388" s="9" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -11005,6 +11398,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F389" s="9" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -11032,6 +11426,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F390" s="9" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -11059,6 +11454,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F391" s="9" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -11086,6 +11482,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F392" s="9" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -11113,6 +11510,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F393" s="9" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -11140,6 +11538,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F394" s="9" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -11167,6 +11566,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F395" s="9" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -11194,6 +11594,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F396" s="9" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -11221,6 +11622,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F397" s="9" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -11248,6 +11650,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F398" s="9" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -11275,6 +11678,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F399" s="9" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -11302,6 +11706,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F400" s="9" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -11329,6 +11734,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F401" s="9" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -11356,6 +11762,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F402" s="9" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -11383,6 +11790,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F403" s="9" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -11410,6 +11818,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F404" s="9" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -11437,6 +11846,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F405" s="9" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -11464,6 +11874,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F406" s="9" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
@@ -11491,6 +11902,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F407" s="9" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -11518,6 +11930,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F408" s="9" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -11545,6 +11958,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F409" s="9" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -11572,6 +11986,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F410" s="9" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -11599,6 +12014,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F411" s="9" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -11626,6 +12042,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F412" s="9" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -11653,6 +12070,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F413" s="9" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -11680,6 +12098,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F414" s="9" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -11707,6 +12126,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F415" s="9" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -11734,6 +12154,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F416" s="9" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -11761,6 +12182,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F417" s="9" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -11788,6 +12210,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F418" s="9" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -11815,6 +12238,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F419" s="9" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -11842,6 +12266,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F420" s="9" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -11869,6 +12294,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F421" s="9" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -11896,6 +12322,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F422" s="9" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -11923,6 +12350,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F423" s="9" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -11950,6 +12378,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F424" s="9" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -11977,6 +12406,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F425" s="9" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -12004,6 +12434,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F426" s="9" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
@@ -12031,6 +12462,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F427" s="9" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -12058,6 +12490,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F428" s="9" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -12085,6 +12518,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F429" s="9" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -12112,6 +12546,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F430" s="9" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -12139,6 +12574,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F431" s="9" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -12166,6 +12602,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F432" s="9" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -12193,6 +12630,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F433" s="9" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -12220,6 +12658,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F434" s="9" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
@@ -12247,6 +12686,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F435" s="9" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -12274,6 +12714,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F436" s="9" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -12301,6 +12742,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F437" s="9" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -12328,6 +12770,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F438" s="9" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -12355,6 +12798,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F439" s="9" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -12382,6 +12826,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F440" s="9" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -12409,6 +12854,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F441" s="9" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -12436,6 +12882,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F442" s="9" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -12463,6 +12910,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F443" s="9" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -12490,6 +12938,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F444" s="9" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -12517,6 +12966,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F445" s="9" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -12544,6 +12994,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F446" s="9" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -12571,6 +13022,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F447" s="9" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -12598,6 +13050,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F448" s="9" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -12625,6 +13078,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F449" s="9" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -12652,6 +13106,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F450" s="9" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -12679,6 +13134,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F451" s="9" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -12706,6 +13162,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F452" s="9" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -12733,6 +13190,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F453" s="9" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -12760,6 +13218,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F454" s="9" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -12787,6 +13246,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F455" s="9" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -12814,6 +13274,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F456" s="9" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -12841,6 +13302,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F457" s="9" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -12868,6 +13330,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F458" s="9" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -12895,6 +13358,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F459" s="9" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -12922,6 +13386,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F460" s="9" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -12949,6 +13414,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F461" s="9" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -12976,6 +13442,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F462" s="9" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
@@ -13003,6 +13470,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F463" s="9" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -13030,6 +13498,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F464" s="9" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -13057,6 +13526,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F465" s="9" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -13084,6 +13554,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F466" s="9" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -13111,6 +13582,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F467" s="9" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -13138,6 +13610,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F468" s="9" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -13165,6 +13638,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F469" s="9" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -13192,6 +13666,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F470" s="9" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -13219,6 +13694,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F471" s="9" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -13246,6 +13722,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F472" s="9" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -13273,6 +13750,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F473" s="9" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -13300,6 +13778,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F474" s="9" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -13327,6 +13806,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F475" s="9" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -13354,6 +13834,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F476" s="9" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
@@ -13381,6 +13862,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F477" s="9" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -13408,6 +13890,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F478" s="9" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -13435,6 +13918,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F479" s="9" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -13462,6 +13946,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F480" s="9" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -13489,6 +13974,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F481" s="9" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -13516,6 +14002,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F482" s="9" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -13543,6 +14030,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F483" s="9" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -13570,6 +14058,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F484" s="9" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -13597,6 +14086,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F485" s="9" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -13624,6 +14114,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F486" s="9" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -13651,6 +14142,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F487" s="9" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -13678,6 +14170,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F488" s="9" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -13705,6 +14198,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F489" s="9" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -13732,6 +14226,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F490" s="9" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
@@ -13759,6 +14254,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F491" s="9" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -13786,6 +14282,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F492" s="9" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -13813,6 +14310,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F493" s="9" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -13840,6 +14338,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F494" s="9" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -13867,6 +14366,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F495" s="9" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -13894,6 +14394,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F496" s="9" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -13921,6 +14422,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F497" s="9" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -13948,6 +14450,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F498" s="9" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -13975,6 +14478,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F499" s="9" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -14002,6 +14506,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F500" s="9" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -14029,6 +14534,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F501" s="9" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -14056,6 +14562,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F502" s="9" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -14083,6 +14590,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F503" s="9" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -14110,6 +14618,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F504" s="9" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
@@ -14137,6 +14646,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F505" s="9" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -14164,6 +14674,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F506" s="9" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -14191,6 +14702,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F507" s="9" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -14218,6 +14730,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F508" s="9" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -14245,6 +14758,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F509" s="9" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -14272,6 +14786,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F510" s="9" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
@@ -14299,6 +14814,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F511" s="9" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -14326,6 +14842,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F512" s="9" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -14353,6 +14870,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F513" s="9" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -14380,6 +14898,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F514" s="9" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -14407,6 +14926,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F515" s="9" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -14434,6 +14954,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F516" s="9" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -14461,6 +14982,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F517" s="9" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -14488,6 +15010,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F518" s="9" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
@@ -14515,6 +15038,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F519" s="9" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -14542,6 +15066,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F520" s="9" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -14569,6 +15094,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F521" s="9" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -14596,6 +15122,7 @@
           <t>BIST</t>
         </is>
       </c>
+      <c r="F522" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E522"/>
